--- a/reporte_inventario.xlsx
+++ b/reporte_inventario.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Alertas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Inventario_Limpio" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="A_Revisar" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Log_Limpieza" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alertas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario_Limpio" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A_Revisar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log_Limpieza" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alertas'!$A$1:$L$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Inventario_Limpio'!$A$1:$L$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alertas'!$A$1:$K$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Inventario_Limpio'!$A$1:$K$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,10 +23,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="167" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -87,7 +88,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -655,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -667,9 +668,8 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -720,15 +720,10 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Valor_Stock</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Valor_Stock</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -772,11 +767,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="3" t="n">
+      <c r="J2" s="3" t="n">
         <v>9900</v>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -820,11 +814,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>4200</v>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -868,11 +861,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>8300</v>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -916,11 +908,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>6400</v>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -964,11 +955,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>19200</v>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1012,11 +1002,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <v>30800</v>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1060,11 +1049,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <v>115500</v>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1108,11 +1096,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="3" t="n">
+      <c r="J9" s="3" t="n">
         <v>37500</v>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1156,11 +1143,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1204,11 +1190,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="3" t="n">
+      <c r="J11" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1252,11 +1237,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="3" t="n">
+      <c r="J12" s="3" t="n">
         <v>12000</v>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1300,11 +1284,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="3" t="n">
+      <c r="J13" s="3" t="n">
         <v>7700</v>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1348,11 +1331,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="3" t="n">
+      <c r="J14" s="3" t="n">
         <v>12000</v>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1396,11 +1378,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="3" t="n">
+      <c r="J15" s="3" t="n">
         <v>8800</v>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1444,11 +1425,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="3" t="n">
+      <c r="J16" s="3" t="n">
         <v>308000</v>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1492,11 +1472,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="3" t="n">
+      <c r="J17" s="3" t="n">
         <v>55800</v>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1540,11 +1519,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="3" t="n">
+      <c r="J18" s="3" t="n">
         <v>19000</v>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1588,11 +1566,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="3" t="n">
+      <c r="J19" s="3" t="n">
         <v>500500</v>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1636,11 +1613,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="3" t="n">
+      <c r="J20" s="3" t="n">
         <v>107900</v>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1684,11 +1660,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="3" t="n">
+      <c r="J21" s="3" t="n">
         <v>162500</v>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1732,11 +1707,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="3" t="n">
+      <c r="J22" s="3" t="n">
         <v>539000</v>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1780,11 +1754,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="3" t="n">
+      <c r="J23" s="3" t="n">
         <v>16500</v>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -1828,11 +1801,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="3" t="n">
+      <c r="J24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="6" t="inlineStr">
+      <c r="K24" s="6" t="inlineStr">
         <is>
           <t>SIN STOCK</t>
         </is>
@@ -1876,18 +1848,17 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="3" t="n">
+      <c r="J25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="6" t="inlineStr">
+      <c r="K25" s="6" t="inlineStr">
         <is>
           <t>SIN STOCK</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L25"/>
+  <autoFilter ref="A1:K25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1898,7 +1869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1910,9 +1881,8 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1963,15 +1933,10 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Valor_Stock</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Valor_Stock</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -2015,11 +1980,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="3" t="n">
+      <c r="J2" s="3" t="n">
         <v>130200</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2063,11 +2027,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>88200</v>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2111,11 +2074,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>460800</v>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2159,11 +2121,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>16500</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -2207,11 +2168,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>98050</v>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2255,11 +2215,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <v>71300</v>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2303,11 +2262,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <v>127200</v>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2351,11 +2309,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="3" t="n">
+      <c r="J9" s="3" t="n">
         <v>31000</v>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2399,11 +2356,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>62700</v>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2447,11 +2403,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="3" t="n">
+      <c r="J11" s="3" t="n">
         <v>460800</v>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2495,11 +2450,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="3" t="n">
+      <c r="J12" s="3" t="n">
         <v>327600</v>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2543,11 +2497,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="3" t="n">
+      <c r="J13" s="3" t="n">
         <v>115500</v>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -2591,11 +2544,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="3" t="n">
+      <c r="J14" s="3" t="n">
         <v>500500</v>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -2639,11 +2591,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="3" t="n">
+      <c r="J15" s="3" t="n">
         <v>57000</v>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2687,11 +2638,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="3" t="n">
+      <c r="J16" s="3" t="n">
         <v>96600</v>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2735,11 +2685,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="3" t="n">
+      <c r="J17" s="3" t="n">
         <v>107900</v>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -2783,11 +2732,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="3" t="n">
+      <c r="J18" s="3" t="n">
         <v>140800</v>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2831,11 +2779,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="3" t="n">
+      <c r="J19" s="3" t="n">
         <v>38400</v>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2879,11 +2826,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="3" t="n">
+      <c r="J20" s="3" t="n">
         <v>84000</v>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2927,11 +2873,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="3" t="n">
+      <c r="J21" s="3" t="n">
         <v>168000</v>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2975,11 +2920,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="3" t="n">
+      <c r="J22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>SIN STOCK</t>
         </is>
@@ -3023,11 +2967,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="3" t="n">
+      <c r="J23" s="3" t="n">
         <v>204000</v>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3071,11 +3014,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="3" t="n">
+      <c r="J24" s="3" t="n">
         <v>316800</v>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3119,11 +3061,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="3" t="n">
+      <c r="J25" s="3" t="n">
         <v>76800</v>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3167,11 +3108,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="3" t="n">
+      <c r="J26" s="3" t="n">
         <v>422400</v>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3215,11 +3155,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="3" t="n">
+      <c r="J27" s="3" t="n">
         <v>24000</v>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3263,11 +3202,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="3" t="n">
+      <c r="J28" s="3" t="n">
         <v>249600</v>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3311,11 +3249,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="3" t="n">
+      <c r="J29" s="3" t="n">
         <v>79500</v>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3359,11 +3296,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="3" t="n">
+      <c r="J30" s="3" t="n">
         <v>55800</v>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -3407,11 +3343,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="3" t="n">
+      <c r="J31" s="3" t="n">
         <v>28800</v>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3455,11 +3390,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="3" t="n">
+      <c r="J32" s="3" t="n">
         <v>343200</v>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3503,11 +3437,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="3" t="n">
+      <c r="J33" s="3" t="n">
         <v>537600</v>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3551,11 +3484,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="3" t="n">
+      <c r="J34" s="3" t="n">
         <v>1617000</v>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3599,11 +3531,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="3" t="n">
+      <c r="J35" s="3" t="n">
         <v>156800</v>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3647,11 +3578,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="3" t="n">
+      <c r="J36" s="3" t="n">
         <v>46250</v>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3695,11 +3625,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="3" t="n">
+      <c r="J37" s="3" t="n">
         <v>9900</v>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -3743,11 +3672,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="3" t="n">
+      <c r="J38" s="3" t="n">
         <v>4200</v>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -3791,11 +3719,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="3" t="n">
+      <c r="J39" s="3" t="n">
         <v>124800</v>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3839,11 +3766,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="3" t="n">
+      <c r="J40" s="3" t="n">
         <v>9200</v>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -3887,11 +3813,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="3" t="n">
+      <c r="J41" s="3" t="n">
         <v>102600</v>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3935,11 +3860,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="3" t="n">
+      <c r="J42" s="3" t="n">
         <v>677600</v>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3983,11 +3907,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="3" t="n">
+      <c r="J43" s="3" t="n">
         <v>528000</v>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4031,11 +3954,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="3" t="n">
+      <c r="J44" s="3" t="n">
         <v>234000</v>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4079,11 +4001,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="3" t="n">
+      <c r="J45" s="3" t="n">
         <v>1617000</v>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4127,11 +4048,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="3" t="n">
+      <c r="J46" s="3" t="n">
         <v>24000</v>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4175,11 +4095,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="3" t="n">
+      <c r="J47" s="3" t="n">
         <v>966000</v>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4223,11 +4142,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="3" t="n">
+      <c r="J48" s="3" t="n">
         <v>161200</v>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4271,11 +4189,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="3" t="n">
+      <c r="J49" s="3" t="n">
         <v>523600</v>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4319,11 +4236,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="3" t="n">
+      <c r="J50" s="3" t="n">
         <v>8300</v>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -4367,11 +4283,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="3" t="n">
+      <c r="J51" s="3" t="n">
         <v>31900</v>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4415,11 +4330,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="3" t="n">
+      <c r="J52" s="3" t="n">
         <v>159600</v>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4463,11 +4377,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="3" t="n">
+      <c r="J53" s="3" t="n">
         <v>138000</v>
       </c>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4511,11 +4424,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="3" t="n">
+      <c r="J54" s="3" t="n">
         <v>412800</v>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4559,11 +4471,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="3" t="n">
+      <c r="J55" s="3" t="n">
         <v>6400</v>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -4607,11 +4518,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="3" t="n">
+      <c r="J56" s="3" t="n">
         <v>135700</v>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4655,11 +4565,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="3" t="n">
+      <c r="J57" s="3" t="n">
         <v>275000</v>
       </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4703,11 +4612,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="3" t="n">
+      <c r="J58" s="3" t="n">
         <v>207500</v>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4751,11 +4659,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="3" t="n">
+      <c r="J59" s="3" t="n">
         <v>525000</v>
       </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4799,11 +4706,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="3" t="n">
+      <c r="J60" s="3" t="n">
         <v>808500</v>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4847,11 +4753,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="3" t="n">
+      <c r="J61" s="3" t="n">
         <v>12000</v>
       </c>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -4895,11 +4800,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="3" t="n">
+      <c r="J62" s="3" t="n">
         <v>45600</v>
       </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4943,11 +4847,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="3" t="n">
+      <c r="J63" s="3" t="n">
         <v>131100</v>
       </c>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4991,11 +4894,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="3" t="n">
+      <c r="J64" s="3" t="n">
         <v>102400</v>
       </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5039,11 +4941,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="3" t="n">
+      <c r="J65" s="3" t="n">
         <v>19200</v>
       </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -5087,11 +4988,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="3" t="n">
+      <c r="J66" s="3" t="n">
         <v>30800</v>
       </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -5135,11 +5035,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="3" t="n">
+      <c r="J67" s="3" t="n">
         <v>96900</v>
       </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5183,11 +5082,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="3" t="n">
+      <c r="J68" s="3" t="n">
         <v>77000</v>
       </c>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5231,11 +5129,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="3" t="n">
+      <c r="J69" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="L69" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -5279,11 +5176,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="3" t="n">
+      <c r="J70" s="3" t="n">
         <v>487500</v>
       </c>
-      <c r="L70" s="2" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5327,11 +5223,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="3" t="n">
+      <c r="J71" s="3" t="n">
         <v>350000</v>
       </c>
-      <c r="L71" s="2" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5375,11 +5270,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="3" t="n">
+      <c r="J72" s="3" t="n">
         <v>468000</v>
       </c>
-      <c r="L72" s="2" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5423,11 +5317,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="3" t="n">
+      <c r="J73" s="3" t="n">
         <v>247500</v>
       </c>
-      <c r="L73" s="2" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5471,11 +5364,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="3" t="n">
+      <c r="J74" s="3" t="n">
         <v>74100</v>
       </c>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5519,11 +5411,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="3" t="n">
+      <c r="J75" s="3" t="n">
         <v>141600</v>
       </c>
-      <c r="L75" s="2" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5567,11 +5458,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="3" t="n">
+      <c r="J76" s="3" t="n">
         <v>104500</v>
       </c>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5615,11 +5505,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="3" t="n">
+      <c r="J77" s="3" t="n">
         <v>103600</v>
       </c>
-      <c r="L77" s="2" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5663,11 +5552,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="3" t="n">
+      <c r="J78" s="3" t="n">
         <v>415000</v>
       </c>
-      <c r="L78" s="2" t="inlineStr">
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5711,11 +5599,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="3" t="n">
+      <c r="J79" s="3" t="n">
         <v>231000</v>
       </c>
-      <c r="L79" s="2" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5759,11 +5646,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="3" t="n">
+      <c r="J80" s="3" t="n">
         <v>326400</v>
       </c>
-      <c r="L80" s="2" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5807,11 +5693,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="3" t="n">
+      <c r="J81" s="3" t="n">
         <v>8800</v>
       </c>
-      <c r="L81" s="2" t="inlineStr">
+      <c r="K81" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -5855,11 +5740,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="3" t="n">
+      <c r="J82" s="3" t="n">
         <v>135700</v>
       </c>
-      <c r="L82" s="2" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5903,11 +5787,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="3" t="n">
+      <c r="J83" s="3" t="n">
         <v>1029000</v>
       </c>
-      <c r="L83" s="2" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5951,11 +5834,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="3" t="n">
+      <c r="J84" s="3" t="n">
         <v>131200</v>
       </c>
-      <c r="L84" s="2" t="inlineStr">
+      <c r="K84" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5999,11 +5881,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr"/>
-      <c r="K85" s="3" t="n">
+      <c r="J85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L85" s="2" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>SIN STOCK</t>
         </is>
@@ -6047,11 +5928,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="3" t="n">
+      <c r="J86" s="3" t="n">
         <v>188700</v>
       </c>
-      <c r="L86" s="2" t="inlineStr">
+      <c r="K86" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6095,11 +5975,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="3" t="n">
+      <c r="J87" s="3" t="n">
         <v>224000</v>
       </c>
-      <c r="L87" s="2" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6143,11 +6022,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="3" t="n">
+      <c r="J88" s="3" t="n">
         <v>162500</v>
       </c>
-      <c r="L88" s="2" t="inlineStr">
+      <c r="K88" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -6191,11 +6069,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="3" t="n">
+      <c r="J89" s="3" t="n">
         <v>25900</v>
       </c>
-      <c r="L89" s="2" t="inlineStr">
+      <c r="K89" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6239,11 +6116,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="3" t="n">
+      <c r="J90" s="3" t="n">
         <v>19000</v>
       </c>
-      <c r="L90" s="2" t="inlineStr">
+      <c r="K90" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -6287,11 +6163,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr"/>
-      <c r="K91" s="3" t="n">
+      <c r="J91" s="3" t="n">
         <v>294400</v>
       </c>
-      <c r="L91" s="2" t="inlineStr">
+      <c r="K91" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6335,11 +6210,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="3" t="n">
+      <c r="J92" s="3" t="n">
         <v>173600</v>
       </c>
-      <c r="L92" s="2" t="inlineStr">
+      <c r="K92" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6383,11 +6257,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr"/>
-      <c r="K93" s="3" t="n">
+      <c r="J93" s="3" t="n">
         <v>12000</v>
       </c>
-      <c r="L93" s="2" t="inlineStr">
+      <c r="K93" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -6431,11 +6304,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr"/>
-      <c r="K94" s="3" t="n">
+      <c r="J94" s="3" t="n">
         <v>37500</v>
       </c>
-      <c r="L94" s="2" t="inlineStr">
+      <c r="K94" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -6479,11 +6351,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr"/>
-      <c r="K95" s="3" t="n">
+      <c r="J95" s="3" t="n">
         <v>105000</v>
       </c>
-      <c r="L95" s="2" t="inlineStr">
+      <c r="K95" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6527,11 +6398,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="3" t="n">
+      <c r="J96" s="3" t="n">
         <v>308000</v>
       </c>
-      <c r="L96" s="2" t="inlineStr">
+      <c r="K96" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -6575,11 +6445,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="3" t="n">
+      <c r="J97" s="3" t="n">
         <v>50400</v>
       </c>
-      <c r="L97" s="2" t="inlineStr">
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6623,11 +6492,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="3" t="n">
+      <c r="J98" s="3" t="n">
         <v>259200</v>
       </c>
-      <c r="L98" s="2" t="inlineStr">
+      <c r="K98" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6671,11 +6539,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr"/>
-      <c r="K99" s="3" t="n">
+      <c r="J99" s="3" t="n">
         <v>98000</v>
       </c>
-      <c r="L99" s="2" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6719,11 +6586,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="3" t="n">
+      <c r="J100" s="3" t="n">
         <v>86800</v>
       </c>
-      <c r="L100" s="2" t="inlineStr">
+      <c r="K100" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6767,11 +6633,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr"/>
-      <c r="K101" s="3" t="n">
+      <c r="J101" s="3" t="n">
         <v>163200</v>
       </c>
-      <c r="L101" s="2" t="inlineStr">
+      <c r="K101" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6815,11 +6680,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr"/>
-      <c r="K102" s="3" t="n">
+      <c r="J102" s="3" t="n">
         <v>147000</v>
       </c>
-      <c r="L102" s="2" t="inlineStr">
+      <c r="K102" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6863,11 +6727,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr"/>
-      <c r="K103" s="3" t="n">
+      <c r="J103" s="3" t="n">
         <v>57600</v>
       </c>
-      <c r="L103" s="2" t="inlineStr">
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6911,11 +6774,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr"/>
-      <c r="K104" s="3" t="n">
+      <c r="J104" s="3" t="n">
         <v>45100</v>
       </c>
-      <c r="L104" s="2" t="inlineStr">
+      <c r="K104" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6959,11 +6821,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr"/>
-      <c r="K105" s="3" t="n">
+      <c r="J105" s="3" t="n">
         <v>188100</v>
       </c>
-      <c r="L105" s="2" t="inlineStr">
+      <c r="K105" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7007,11 +6868,10 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr"/>
-      <c r="K106" s="3" t="n">
+      <c r="J106" s="3" t="n">
         <v>52900</v>
       </c>
-      <c r="L106" s="2" t="inlineStr">
+      <c r="K106" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7055,11 +6915,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr"/>
-      <c r="K107" s="3" t="n">
+      <c r="J107" s="3" t="n">
         <v>7700</v>
       </c>
-      <c r="L107" s="2" t="inlineStr">
+      <c r="K107" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -7103,11 +6962,10 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr"/>
-      <c r="K108" s="3" t="n">
+      <c r="J108" s="3" t="n">
         <v>76500</v>
       </c>
-      <c r="L108" s="2" t="inlineStr">
+      <c r="K108" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7151,11 +7009,10 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr"/>
-      <c r="K109" s="3" t="n">
+      <c r="J109" s="3" t="n">
         <v>51300</v>
       </c>
-      <c r="L109" s="2" t="inlineStr">
+      <c r="K109" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7199,11 +7056,10 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr"/>
-      <c r="K110" s="3" t="n">
+      <c r="J110" s="3" t="n">
         <v>451200</v>
       </c>
-      <c r="L110" s="2" t="inlineStr">
+      <c r="K110" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7247,11 +7103,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr"/>
-      <c r="K111" s="3" t="n">
+      <c r="J111" s="3" t="n">
         <v>539000</v>
       </c>
-      <c r="L111" s="2" t="inlineStr">
+      <c r="K111" s="2" t="inlineStr">
         <is>
           <t>STOCK BAJO</t>
         </is>
@@ -7295,11 +7150,10 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr"/>
-      <c r="K112" s="3" t="n">
+      <c r="J112" s="3" t="n">
         <v>227700</v>
       </c>
-      <c r="L112" s="2" t="inlineStr">
+      <c r="K112" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7343,18 +7197,17 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr"/>
-      <c r="K113" s="3" t="n">
+      <c r="J113" s="3" t="n">
         <v>1886500</v>
       </c>
-      <c r="L113" s="2" t="inlineStr">
+      <c r="K113" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L113"/>
+  <autoFilter ref="A1:K113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
